--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487529_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487529_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9268</v>
+        <v>6.0502</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9872</v>
+        <v>5.0037</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9396</v>
+        <v>1.0465</v>
       </c>
       <c r="G2" t="n">
         <v>5.7738</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0268</v>
+        <v>-0.9034</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2041</v>
+        <v>-0.1876</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8227</v>
+        <v>-0.7158</v>
       </c>
       <c r="V2" t="n">
         <v>1.7673</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5735</v>
+        <v>0.2978</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8056</v>
+        <v>1.3962</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.232</v>
+        <v>-1.0984</v>
       </c>
       <c r="G3" t="n">
         <v>0.7508</v>
@@ -688,13 +688,13 @@
         <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0232</v>
+        <v>-0.2525</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7287</v>
+        <v>0.3194</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7055</v>
+        <v>-0.5718</v>
       </c>
       <c r="V3" t="n">
         <v>-1.7673</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006</v>
+        <v>0.1618</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0984</v>
+        <v>0.0039</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1044</v>
+        <v>0.1578</v>
       </c>
       <c r="G4" t="n">
         <v>0.3621</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3561</v>
+        <v>-0.2003</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2373</v>
+        <v>-0.1838</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1726</v>
+        <v>-0.3133</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0914</v>
+        <v>-1.339</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9187</v>
+        <v>1.0257</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4695</v>
@@ -844,13 +844,13 @@
         <v>1.9585</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3863</v>
+        <v>-0.527</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1059</v>
+        <v>-0.1417</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4921</v>
+        <v>-0.3852</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2754</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0818</v>
+        <v>-0.7232</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0689</v>
+        <v>-1.336</v>
       </c>
       <c r="F6" t="n">
-        <v>0.987</v>
+        <v>0.6128</v>
       </c>
       <c r="G6" t="n">
         <v>1.9106</v>
@@ -922,13 +922,13 @@
         <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5271</v>
+        <v>-0.1685</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2474</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7204</v>
+        <v>0.3461</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1152</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2961</v>
+        <v>-0.897</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4851</v>
+        <v>-1.0593</v>
       </c>
       <c r="F7" t="n">
-        <v>0.189</v>
+        <v>0.1623</v>
       </c>
       <c r="G7" t="n">
         <v>2.8519</v>
@@ -1000,13 +1000,13 @@
         <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3646</v>
+        <v>-0.9656</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5299</v>
+        <v>-0.1041</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8347</v>
+        <v>-0.8615</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2166</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5423</v>
+        <v>-2.0969</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0613</v>
+        <v>-1.6159</v>
       </c>
       <c r="F8" t="n">
         <v>-0.481</v>
@@ -1078,10 +1078,10 @@
         <v>2.1543</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.22</v>
+        <v>-0.7746</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5375</v>
+        <v>-0.0171</v>
       </c>
       <c r="U8" t="n">
         <v>-0.7575</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.532</v>
+        <v>-3.1993</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.5396</v>
+        <v>-4.4208</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0077</v>
+        <v>1.2215</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6149</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1129</v>
+        <v>-1.7803</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8446</v>
+        <v>-0.7258</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2684</v>
+        <v>-1.0545</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7093</v>
+        <v>-4.5138</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7602</v>
+        <v>-4.3509</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0509</v>
+        <v>-0.1629</v>
       </c>
       <c r="G10" t="n">
         <v>0.3216</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2694</v>
+        <v>-1.0739</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9328</v>
+        <v>-0.5234</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3366</v>
+        <v>-0.5505</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6071</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8278</v>
+        <v>-5.233700000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.312100000000001</v>
+        <v>-7.718099999999998</v>
       </c>
       <c r="F11" t="n">
         <v>2.4843</v>
@@ -1312,13 +1312,13 @@
         <v>13.7093</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.240000000000001</v>
+        <v>-6.646100000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.5055</v>
+        <v>-1.9114</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.7344</v>
+        <v>-4.734499999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-4.430899999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.2511</v>
+        <v>12.9738</v>
       </c>
       <c r="E12" t="n">
-        <v>8.1477</v>
+        <v>8.25</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1034</v>
+        <v>4.7238</v>
       </c>
       <c r="G12" t="n">
         <v>6.9701</v>
@@ -1390,13 +1390,13 @@
         <v>2.7419</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3616</v>
+        <v>1.0844</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2117</v>
+        <v>0.3141</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1499</v>
+        <v>0.7703</v>
       </c>
       <c r="V12" t="n">
         <v>3.1567</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8032</v>
+        <v>2.5715</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5009</v>
+        <v>-1.5243</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3041</v>
+        <v>4.0958</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9146</v>
@@ -1468,13 +1468,13 @@
         <v>2.546</v>
       </c>
       <c r="S13" t="n">
-        <v>3.288</v>
+        <v>2.0564</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1573</v>
+        <v>1.1339</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1308</v>
+        <v>0.9225</v>
       </c>
       <c r="V13" t="n">
         <v>0.8837</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3278</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0975</v>
+        <v>-0.3623</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2303</v>
+        <v>-0.4931</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5224</v>
+        <v>-0.85</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7201</v>
+        <v>-0.7339</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1976</v>
+        <v>-0.1161</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0181</v>
+        <v>0.7687</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0223</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0404</v>
+        <v>0.6871</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5406</v>
+        <v>-1.6187</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6978</v>
+        <v>-0.8156</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1572</v>
+        <v>-0.8031</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.7626</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1543</v>
+        <v>0.5875</v>
       </c>
       <c r="S14" t="n">
-        <v>5.2212</v>
+        <v>0.0534</v>
       </c>
       <c r="T14" t="n">
-        <v>4.721</v>
+        <v>-0.1517</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5002</v>
+        <v>0.2051</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6083</v>
+        <v>0.3329</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8837</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.2232</v>
+        <v>-0.8993</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5669</v>
+        <v>-2.9341</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6562</v>
+        <v>2.0348</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.85</v>
+        <v>-1.3262</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7339</v>
+        <v>-1.0133</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1161</v>
+        <v>-0.3129</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7687</v>
+        <v>-1.0762</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.2075</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6871</v>
+        <v>-1.2836</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6187</v>
+        <v>-0.25</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8156</v>
+        <v>-1.2207</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8031</v>
+        <v>0.9707</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5875</v>
+        <v>2.546</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3145</v>
+        <v>0.3901</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3564</v>
+        <v>0.1006</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0419</v>
+        <v>0.2895</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3329</v>
+        <v>-0.5507</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3329</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9887</v>
+        <v>-1.3479</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8762</v>
+        <v>-0.2622</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1124</v>
+        <v>-1.0857</v>
       </c>
       <c r="G16" t="n">
         <v>-3.1429</v>
@@ -1702,13 +1702,13 @@
         <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1543</v>
+        <v>0.795</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0047</v>
+        <v>0.6187</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1496</v>
+        <v>0.1763</v>
       </c>
       <c r="V16" t="n">
         <v>0.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>J. NGUFOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0848</v>
+        <v>-1.4015</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.4458</v>
+        <v>-1.0064</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3609</v>
+        <v>-0.395</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3262</v>
+        <v>-2.3139</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0133</v>
+        <v>0.5812</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3129</v>
+        <v>-2.8951</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0762</v>
+        <v>-1.1816</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2075</v>
+        <v>0.1021</v>
       </c>
       <c r="L17" t="n">
         <v>-1.2836</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.25</v>
+        <v>-1.1323</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2207</v>
+        <v>0.4791</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9707</v>
+        <v>-1.6114</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5875</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>2.546</v>
+        <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7955</v>
+        <v>0.8709</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4111</v>
+        <v>0.6417</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3843</v>
+        <v>0.2292</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5507</v>
+        <v>1.2166</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5507</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NGUFOR</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4857</v>
+        <v>-1.7736</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9275</v>
+        <v>-1.8703</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5582</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3139</v>
+        <v>-1.5224</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5812</v>
+        <v>-1.7201</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8951</v>
+        <v>0.1976</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1816</v>
+        <v>0.0181</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1021</v>
+        <v>-0.0223</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2836</v>
+        <v>0.0404</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1323</v>
+        <v>-1.5406</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4791</v>
+        <v>-1.6978</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6114</v>
+        <v>0.1572</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1751</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>2.1543</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2133</v>
+        <v>2.1198</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2794</v>
+        <v>1.7532</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.3666</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2166</v>
+        <v>-0.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>1.492</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2754</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.772</v>
+        <v>-2.0756</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.4123</v>
+        <v>-2.7749</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6403</v>
+        <v>0.6993</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7018</v>
@@ -1936,13 +1936,13 @@
         <v>2.9377</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4619</v>
+        <v>1.2345</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3133</v>
+        <v>0.3241</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8514</v>
+        <v>0.9104</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6083</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>5.8277</v>
+        <v>7.192100000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.484399999999999</v>
+        <v>-2.4845</v>
       </c>
       <c r="F20" t="n">
-        <v>8.312199999999999</v>
+        <v>9.676600000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-7.801699999999999</v>
@@ -2002,7 +2002,7 @@
         <v>-7.4527</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8379999999999996</v>
+        <v>0.8380000000000001</v>
       </c>
       <c r="P20" t="n">
         <v>1.9584</v>
@@ -2014,19 +2014,19 @@
         <v>15.6677</v>
       </c>
       <c r="S20" t="n">
-        <v>7.2399</v>
+        <v>8.604500000000002</v>
       </c>
       <c r="T20" t="n">
-        <v>4.734500000000001</v>
+        <v>4.7346</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5056</v>
+        <v>3.8699</v>
       </c>
       <c r="V20" t="n">
         <v>4.4309</v>
       </c>
       <c r="W20" t="n">
-        <v>7.677699999999999</v>
+        <v>7.6777</v>
       </c>
       <c r="X20" t="n">
         <v>-3.2468</v>
